--- a/test-harness/.tmp/export-events.xlsx
+++ b/test-harness/.tmp/export-events.xlsx
@@ -1537,18 +1537,18 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Kissy Town CHP</v>
+        <v>Nekabo CHC</v>
       </c>
       <c r="B79" t="str">
-        <v>lmNWdmeOYmV</v>
+        <v>L4Tw4NlaMjn</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Nekabo CHC</v>
+        <v>Kissy Town CHP</v>
       </c>
       <c r="B80" t="str">
-        <v>L4Tw4NlaMjn</v>
+        <v>lmNWdmeOYmV</v>
       </c>
     </row>
     <row r="81">
@@ -1777,18 +1777,18 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Yemoh Town CHC</v>
+        <v>Stella Maries Clinic</v>
       </c>
       <c r="B109" t="str">
-        <v>RhJbg8UD75Q</v>
+        <v>Ea3j0kUvyWg</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Stella Maries Clinic</v>
+        <v>Yemoh Town CHC</v>
       </c>
       <c r="B110" t="str">
-        <v>Ea3j0kUvyWg</v>
+        <v>RhJbg8UD75Q</v>
       </c>
     </row>
     <row r="111">
@@ -1961,18 +1961,18 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Woyama MCHP</v>
+        <v>Kaponkie MCHP</v>
       </c>
       <c r="B132" t="str">
-        <v>fPe1l06MurL</v>
+        <v>Crgx572DnXR</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Kaponkie MCHP</v>
+        <v>Woyama MCHP</v>
       </c>
       <c r="B133" t="str">
-        <v>Crgx572DnXR</v>
+        <v>fPe1l06MurL</v>
       </c>
     </row>
     <row r="134">
@@ -2017,18 +2017,18 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Small Sefadu MCHP</v>
+        <v>Masankoro MCHP</v>
       </c>
       <c r="B139" t="str">
-        <v>ncGs9vXS36w</v>
+        <v>l3jnkNNpoD8</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Masankoro MCHP</v>
+        <v>Small Sefadu MCHP</v>
       </c>
       <c r="B140" t="str">
-        <v>l3jnkNNpoD8</v>
+        <v>ncGs9vXS36w</v>
       </c>
     </row>
     <row r="141">
@@ -2697,18 +2697,18 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Magbassabana MCHP</v>
+        <v>Bumpeh River CHP</v>
       </c>
       <c r="B224" t="str">
-        <v>bf6PXrSNMKK</v>
+        <v>mkIugjeYSjE</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Bumpeh River CHP</v>
+        <v>Magbassabana MCHP</v>
       </c>
       <c r="B225" t="str">
-        <v>mkIugjeYSjE</v>
+        <v>bf6PXrSNMKK</v>
       </c>
     </row>
     <row r="226">
@@ -3337,18 +3337,18 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Fatibra CHP</v>
+        <v>Mercy Ship ACFC</v>
       </c>
       <c r="B304" t="str">
-        <v>jfV49JGnYKF</v>
+        <v>xO9WbCvFq5k</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Mercy Ship ACFC</v>
+        <v>Fatibra CHP</v>
       </c>
       <c r="B305" t="str">
-        <v>xO9WbCvFq5k</v>
+        <v>jfV49JGnYKF</v>
       </c>
     </row>
     <row r="306">
@@ -3609,18 +3609,18 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Dankawalie MCHP</v>
+        <v>Mabayo MCHP</v>
       </c>
       <c r="B338" t="str">
-        <v>DErmFP7bri7</v>
+        <v>Xzxy8NuVsLp</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Mabayo MCHP</v>
+        <v>Dankawalie MCHP</v>
       </c>
       <c r="B339" t="str">
-        <v>Xzxy8NuVsLp</v>
+        <v>DErmFP7bri7</v>
       </c>
     </row>
     <row r="340">
@@ -3721,18 +3721,18 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Hill Station MCHP</v>
+        <v>Koidu Under Five Clinic</v>
       </c>
       <c r="B352" t="str">
-        <v>AKvgfYx5WZq</v>
+        <v>Ls2ESQONh9S</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Koidu Under Five Clinic</v>
+        <v>Hill Station MCHP</v>
       </c>
       <c r="B353" t="str">
-        <v>Ls2ESQONh9S</v>
+        <v>AKvgfYx5WZq</v>
       </c>
     </row>
     <row r="354">
@@ -3921,18 +3921,18 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Saahun (kpaka) MCHP</v>
+        <v>Gbonkonka CHP</v>
       </c>
       <c r="B377" t="str">
-        <v>BG2fC2mRFOL</v>
+        <v>v2vi8UaIYlo</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Gbonkonka CHP</v>
+        <v>Saahun (kpaka) MCHP</v>
       </c>
       <c r="B378" t="str">
-        <v>v2vi8UaIYlo</v>
+        <v>BG2fC2mRFOL</v>
       </c>
     </row>
     <row r="379">
@@ -5289,18 +5289,18 @@
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Yoni CHC</v>
+        <v>Mayombo MCHP</v>
       </c>
       <c r="B548" t="str">
-        <v>fAsj6a4nudH</v>
+        <v>gfk1TNPI4wN</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Mayombo MCHP</v>
+        <v>Yoni CHC</v>
       </c>
       <c r="B549" t="str">
-        <v>gfk1TNPI4wN</v>
+        <v>fAsj6a4nudH</v>
       </c>
     </row>
     <row r="550">
@@ -5569,18 +5569,18 @@
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Madina (BUM) CHC</v>
+        <v>kamba mamudia</v>
       </c>
       <c r="B583" t="str">
-        <v>gE3gEGZbQMi</v>
+        <v>zO5hgxxfU4T</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>kamba mamudia</v>
+        <v>Madina (BUM) CHC</v>
       </c>
       <c r="B584" t="str">
-        <v>zO5hgxxfU4T</v>
+        <v>gE3gEGZbQMi</v>
       </c>
     </row>
     <row r="585">
@@ -6969,18 +6969,18 @@
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>Gbahama (Makpele) MCHP</v>
+        <v>St. Luke's Wellington</v>
       </c>
       <c r="B758" t="str">
-        <v>TWH05Rjz6oT</v>
+        <v>vxa2YQRGV7I</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>St. Luke's Wellington</v>
+        <v>Gbahama (Makpele) MCHP</v>
       </c>
       <c r="B759" t="str">
-        <v>vxa2YQRGV7I</v>
+        <v>TWH05Rjz6oT</v>
       </c>
     </row>
     <row r="760">
@@ -7121,18 +7121,18 @@
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>Ngiehun (Lower Bambara) MCHP</v>
+        <v>Kpayama 1 MCHP</v>
       </c>
       <c r="B777" t="str">
-        <v>m21WB5iqHAb</v>
+        <v>So2b8zJfcMa</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>Kpayama 1 MCHP</v>
+        <v>Ngiehun (Lower Bambara) MCHP</v>
       </c>
       <c r="B778" t="str">
-        <v>So2b8zJfcMa</v>
+        <v>m21WB5iqHAb</v>
       </c>
     </row>
     <row r="779">
@@ -7161,18 +7161,18 @@
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>Sandaru (Gaura) MCHP</v>
+        <v>Gbindi CHP</v>
       </c>
       <c r="B782" t="str">
-        <v>hTGeTrwzrPi</v>
+        <v>LFpl1falVZi</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>Gbindi CHP</v>
+        <v>Sandaru (Gaura) MCHP</v>
       </c>
       <c r="B783" t="str">
-        <v>LFpl1falVZi</v>
+        <v>hTGeTrwzrPi</v>
       </c>
     </row>
     <row r="784">
@@ -7209,18 +7209,18 @@
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>Torkpumbu MCHP</v>
+        <v>Mandema CHP</v>
       </c>
       <c r="B788" t="str">
-        <v>RJpiHpefEUw</v>
+        <v>WerHl8SDtRU</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>Mandema CHP</v>
+        <v>Torkpumbu MCHP</v>
       </c>
       <c r="B789" t="str">
-        <v>WerHl8SDtRU</v>
+        <v>RJpiHpefEUw</v>
       </c>
     </row>
     <row r="790">
@@ -7681,18 +7681,18 @@
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>Sienga CHP</v>
+        <v>Needy CHC</v>
       </c>
       <c r="B847" t="str">
-        <v>a1E6QWBTEwX</v>
+        <v>UOJlcpPnBat</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>Needy CHC</v>
+        <v>Sienga CHP</v>
       </c>
       <c r="B848" t="str">
-        <v>UOJlcpPnBat</v>
+        <v>a1E6QWBTEwX</v>
       </c>
     </row>
     <row r="849">
@@ -7873,18 +7873,18 @@
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>SLRCS (Freetown) Clinic</v>
+        <v>Konjo MCHP</v>
       </c>
       <c r="B871" t="str">
-        <v>EmTN0L4EAVi</v>
+        <v>d7hw1ababST</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>Konjo MCHP</v>
+        <v>SLRCS (Freetown) Clinic</v>
       </c>
       <c r="B872" t="str">
-        <v>d7hw1ababST</v>
+        <v>EmTN0L4EAVi</v>
       </c>
     </row>
     <row r="873">
@@ -8761,26 +8761,26 @@
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>Gloucester CHP</v>
+        <v>Mabang MCHP</v>
       </c>
       <c r="B982" t="str">
-        <v>HTDuY3uxj6u</v>
+        <v>fCFdj2T0Bq1</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>Mabang MCHP</v>
+        <v>Mano Yorgbo MCHP</v>
       </c>
       <c r="B983" t="str">
-        <v>fCFdj2T0Bq1</v>
+        <v>KvE0PYQzXMM</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>Mano Yorgbo MCHP</v>
+        <v>Gloucester CHP</v>
       </c>
       <c r="B984" t="str">
-        <v>KvE0PYQzXMM</v>
+        <v>HTDuY3uxj6u</v>
       </c>
     </row>
     <row r="985">
@@ -9289,18 +9289,18 @@
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>Rolembray MCHP</v>
+        <v>Komendeh (Nongowa) MCHP</v>
       </c>
       <c r="B1048" t="str">
-        <v>nZblzPvJ5UW</v>
+        <v>NqwvaQC1ni4</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>Komendeh (Nongowa) MCHP</v>
+        <v>Rolembray MCHP</v>
       </c>
       <c r="B1049" t="str">
-        <v>NqwvaQC1ni4</v>
+        <v>nZblzPvJ5UW</v>
       </c>
     </row>
     <row r="1050">
@@ -9665,18 +9665,18 @@
     </row>
     <row r="1095">
       <c r="A1095" t="str">
-        <v>Tonko Maternity Clinic</v>
+        <v>Gbalan Thallan MCHP</v>
       </c>
       <c r="B1095" t="str">
-        <v>uNEhNuBUr0i</v>
+        <v>FsunWIQLXoF</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="str">
-        <v>Gbalan Thallan MCHP</v>
+        <v>Tonko Maternity Clinic</v>
       </c>
       <c r="B1096" t="str">
-        <v>FsunWIQLXoF</v>
+        <v>uNEhNuBUr0i</v>
       </c>
     </row>
     <row r="1097">
@@ -9881,18 +9881,18 @@
     </row>
     <row r="1122">
       <c r="A1122" t="str">
-        <v>Under Fives Clinic</v>
+        <v>Mattru UBC Hospital</v>
       </c>
       <c r="B1122" t="str">
-        <v>mTNOoGXuC39</v>
+        <v>ctN0WgIvfke</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="str">
-        <v>Mattru UBC Hospital</v>
+        <v>Under Fives Clinic</v>
       </c>
       <c r="B1123" t="str">
-        <v>ctN0WgIvfke</v>
+        <v>mTNOoGXuC39</v>
       </c>
     </row>
     <row r="1124">
@@ -9953,18 +9953,18 @@
     </row>
     <row r="1131">
       <c r="A1131" t="str">
-        <v>Lion for Lion Clinic</v>
+        <v>Gbongeima MCHP</v>
       </c>
       <c r="B1131" t="str">
-        <v>cZxP4NE5O9z</v>
+        <v>rebbn0ooFSO</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="str">
-        <v>Gbongeima MCHP</v>
+        <v>Lion for Lion Clinic</v>
       </c>
       <c r="B1132" t="str">
-        <v>rebbn0ooFSO</v>
+        <v>cZxP4NE5O9z</v>
       </c>
     </row>
     <row r="1133">
@@ -10161,18 +10161,18 @@
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>Magbeni MCHP</v>
+        <v>Kombilie MCHP</v>
       </c>
       <c r="B1157" t="str">
-        <v>UJ80rknbJtm</v>
+        <v>HC2NlwpoXfb</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="str">
-        <v>Kombilie MCHP</v>
+        <v>Magbeni MCHP</v>
       </c>
       <c r="B1158" t="str">
-        <v>HC2NlwpoXfb</v>
+        <v>UJ80rknbJtm</v>
       </c>
     </row>
     <row r="1159">

--- a/test-harness/.tmp/export-events.xlsx
+++ b/test-harness/.tmp/export-events.xlsx
@@ -945,18 +945,18 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Matoto MCHP</v>
+        <v>Masselleh MCHP</v>
       </c>
       <c r="B5" t="str">
-        <v>uGa5JtIMfRx</v>
+        <v>cag6vQQ9SQk</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Masselleh MCHP</v>
+        <v>Matoto MCHP</v>
       </c>
       <c r="B6" t="str">
-        <v>cag6vQQ9SQk</v>
+        <v>uGa5JtIMfRx</v>
       </c>
     </row>
     <row r="7">
@@ -1305,18 +1305,18 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Timbo CHP</v>
+        <v>SLRC (Mattru) Clinic</v>
       </c>
       <c r="B50" t="str">
-        <v>svCLFkT99Yx</v>
+        <v>T2Cn45nBY0u</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SLRC (Mattru) Clinic</v>
+        <v>Timbo CHP</v>
       </c>
       <c r="B51" t="str">
-        <v>T2Cn45nBY0u</v>
+        <v>svCLFkT99Yx</v>
       </c>
     </row>
     <row r="52">
@@ -1345,18 +1345,18 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Banana Island MCHP</v>
+        <v>Rofutha MCHP</v>
       </c>
       <c r="B55" t="str">
-        <v>jjtzkzrmG7s</v>
+        <v>G5FuODAbH6X</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Rofutha MCHP</v>
+        <v>Banana Island MCHP</v>
       </c>
       <c r="B56" t="str">
-        <v>G5FuODAbH6X</v>
+        <v>jjtzkzrmG7s</v>
       </c>
     </row>
     <row r="57">
@@ -1537,18 +1537,18 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Nekabo CHC</v>
+        <v>Kissy Town CHP</v>
       </c>
       <c r="B79" t="str">
-        <v>L4Tw4NlaMjn</v>
+        <v>lmNWdmeOYmV</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Kissy Town CHP</v>
+        <v>Nekabo CHC</v>
       </c>
       <c r="B80" t="str">
-        <v>lmNWdmeOYmV</v>
+        <v>L4Tw4NlaMjn</v>
       </c>
     </row>
     <row r="81">
@@ -1777,18 +1777,18 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Stella Maries Clinic</v>
+        <v>Yemoh Town CHC</v>
       </c>
       <c r="B109" t="str">
-        <v>Ea3j0kUvyWg</v>
+        <v>RhJbg8UD75Q</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Yemoh Town CHC</v>
+        <v>Stella Maries Clinic</v>
       </c>
       <c r="B110" t="str">
-        <v>RhJbg8UD75Q</v>
+        <v>Ea3j0kUvyWg</v>
       </c>
     </row>
     <row r="111">
@@ -1841,18 +1841,18 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Minah MCHP</v>
+        <v>Mogbasske CHP</v>
       </c>
       <c r="B117" t="str">
-        <v>ZW3XCXXiLcO</v>
+        <v>DZaJmtlaBMl</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Mogbasske CHP</v>
+        <v>Minah MCHP</v>
       </c>
       <c r="B118" t="str">
-        <v>DZaJmtlaBMl</v>
+        <v>ZW3XCXXiLcO</v>
       </c>
     </row>
     <row r="119">
@@ -1961,26 +1961,26 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Kaponkie MCHP</v>
+        <v>Woyama MCHP</v>
       </c>
       <c r="B132" t="str">
-        <v>Crgx572DnXR</v>
+        <v>fPe1l06MurL</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Woyama MCHP</v>
+        <v>Mabora MCHP</v>
       </c>
       <c r="B133" t="str">
-        <v>fPe1l06MurL</v>
+        <v>fmkqsEx6MRo</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Mabora MCHP</v>
+        <v>Kaponkie MCHP</v>
       </c>
       <c r="B134" t="str">
-        <v>fmkqsEx6MRo</v>
+        <v>Crgx572DnXR</v>
       </c>
     </row>
     <row r="135">
@@ -2017,18 +2017,18 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Masankoro MCHP</v>
+        <v>Small Sefadu MCHP</v>
       </c>
       <c r="B139" t="str">
-        <v>l3jnkNNpoD8</v>
+        <v>ncGs9vXS36w</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Small Sefadu MCHP</v>
+        <v>Masankoro MCHP</v>
       </c>
       <c r="B140" t="str">
-        <v>ncGs9vXS36w</v>
+        <v>l3jnkNNpoD8</v>
       </c>
     </row>
     <row r="141">
@@ -2089,18 +2089,18 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Scan Drive MCHP</v>
+        <v>Kokoru CHP</v>
       </c>
       <c r="B148" t="str">
-        <v>u1eQDDtKqm7</v>
+        <v>F2TAF765q1b</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Kokoru CHP</v>
+        <v>Scan Drive MCHP</v>
       </c>
       <c r="B149" t="str">
-        <v>F2TAF765q1b</v>
+        <v>u1eQDDtKqm7</v>
       </c>
     </row>
     <row r="150">
@@ -2145,18 +2145,18 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Bambawolo CHP</v>
+        <v>Madina (Malema) MCHP</v>
       </c>
       <c r="B155" t="str">
-        <v>TNbHYOuQi8s</v>
+        <v>SFQigiC2ISS</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Madina (Malema) MCHP</v>
+        <v>Bambawolo CHP</v>
       </c>
       <c r="B156" t="str">
-        <v>SFQigiC2ISS</v>
+        <v>TNbHYOuQi8s</v>
       </c>
     </row>
     <row r="157">
@@ -2305,18 +2305,18 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Masongbo CHC</v>
+        <v>Mabineh MCHP</v>
       </c>
       <c r="B175" t="str">
-        <v>uRQj8WRK0Py</v>
+        <v>mc3jvzpzSi4</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Mabineh MCHP</v>
+        <v>Masongbo CHC</v>
       </c>
       <c r="B176" t="str">
-        <v>mc3jvzpzSi4</v>
+        <v>uRQj8WRK0Py</v>
       </c>
     </row>
     <row r="177">
@@ -2521,18 +2521,18 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Masumbrie MCHP</v>
+        <v>Worreh MCHP</v>
       </c>
       <c r="B202" t="str">
-        <v>flJbtXOQ4ha</v>
+        <v>VSwnkMSAdp7</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Worreh MCHP</v>
+        <v>Masumbrie MCHP</v>
       </c>
       <c r="B203" t="str">
-        <v>VSwnkMSAdp7</v>
+        <v>flJbtXOQ4ha</v>
       </c>
     </row>
     <row r="204">
@@ -2609,18 +2609,18 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Mamanso Kafla MCHP</v>
+        <v>Kindoyal Hospital</v>
       </c>
       <c r="B213" t="str">
-        <v>T1lTKu6zkHN</v>
+        <v>uROAmk9ymNE</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Kindoyal Hospital</v>
+        <v>Mamanso Kafla MCHP</v>
       </c>
       <c r="B214" t="str">
-        <v>uROAmk9ymNE</v>
+        <v>T1lTKu6zkHN</v>
       </c>
     </row>
     <row r="215">
@@ -2689,26 +2689,26 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Kanekor MCHP</v>
+        <v>Magbassabana MCHP</v>
       </c>
       <c r="B223" t="str">
-        <v>tXL6C7P0ObJ</v>
+        <v>bf6PXrSNMKK</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Bumpeh River CHP</v>
+        <v>Kanekor MCHP</v>
       </c>
       <c r="B224" t="str">
-        <v>mkIugjeYSjE</v>
+        <v>tXL6C7P0ObJ</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Magbassabana MCHP</v>
+        <v>Bumpeh River CHP</v>
       </c>
       <c r="B225" t="str">
-        <v>bf6PXrSNMKK</v>
+        <v>mkIugjeYSjE</v>
       </c>
     </row>
     <row r="226">
@@ -2777,18 +2777,18 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Delken MCHP</v>
+        <v>Jangalor MCHP</v>
       </c>
       <c r="B234" t="str">
-        <v>sSgOnY1Xqd9</v>
+        <v>qzm5ww3U0vz</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Jangalor MCHP</v>
+        <v>Delken MCHP</v>
       </c>
       <c r="B235" t="str">
-        <v>qzm5ww3U0vz</v>
+        <v>sSgOnY1Xqd9</v>
       </c>
     </row>
     <row r="236">
@@ -3121,18 +3121,18 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Numea CHC</v>
+        <v>Tongoro MCHP</v>
       </c>
       <c r="B277" t="str">
-        <v>PduUQmdt0pB</v>
+        <v>iIpPPnnzDo6</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Tongoro MCHP</v>
+        <v>Numea CHC</v>
       </c>
       <c r="B278" t="str">
-        <v>iIpPPnnzDo6</v>
+        <v>PduUQmdt0pB</v>
       </c>
     </row>
     <row r="279">
@@ -3217,34 +3217,34 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Senjekoro MCHP</v>
+        <v>Bo Govt. Hosp.</v>
       </c>
       <c r="B289" t="str">
-        <v>tcEjL7gmFJL</v>
+        <v>rZxk3S0qN63</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Bo Govt. Hosp.</v>
+        <v>Senjekoro MCHP</v>
       </c>
       <c r="B290" t="str">
-        <v>rZxk3S0qN63</v>
+        <v>tcEjL7gmFJL</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>UFC Bonthe</v>
+        <v>Tonkomba MCHP</v>
       </c>
       <c r="B291" t="str">
-        <v>gGv9ATEs68L</v>
+        <v>xIMxph4NMP1</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Tonkomba MCHP</v>
+        <v>UFC Bonthe</v>
       </c>
       <c r="B292" t="str">
-        <v>xIMxph4NMP1</v>
+        <v>gGv9ATEs68L</v>
       </c>
     </row>
     <row r="293">
@@ -3337,18 +3337,18 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Mercy Ship ACFC</v>
+        <v>Fatibra CHP</v>
       </c>
       <c r="B304" t="str">
-        <v>xO9WbCvFq5k</v>
+        <v>jfV49JGnYKF</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Fatibra CHP</v>
+        <v>Mercy Ship ACFC</v>
       </c>
       <c r="B305" t="str">
-        <v>jfV49JGnYKF</v>
+        <v>xO9WbCvFq5k</v>
       </c>
     </row>
     <row r="306">
@@ -3585,18 +3585,18 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Makobeh MCHP</v>
+        <v>Yataya CHP</v>
       </c>
       <c r="B335" t="str">
-        <v>iMDr2FG7i8Q</v>
+        <v>MErVkzdbsP5</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Yataya CHP</v>
+        <v>Makobeh MCHP</v>
       </c>
       <c r="B336" t="str">
-        <v>MErVkzdbsP5</v>
+        <v>iMDr2FG7i8Q</v>
       </c>
     </row>
     <row r="337">
@@ -3609,18 +3609,18 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Mabayo MCHP</v>
+        <v>Dankawalie MCHP</v>
       </c>
       <c r="B338" t="str">
-        <v>Xzxy8NuVsLp</v>
+        <v>DErmFP7bri7</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Dankawalie MCHP</v>
+        <v>Mabayo MCHP</v>
       </c>
       <c r="B339" t="str">
-        <v>DErmFP7bri7</v>
+        <v>Xzxy8NuVsLp</v>
       </c>
     </row>
     <row r="340">
@@ -3681,18 +3681,18 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Masamboi MCHP</v>
+        <v>Gbetema MCHP (Fiama)</v>
       </c>
       <c r="B347" t="str">
-        <v>Hu31NCRjZlj</v>
+        <v>as1dnmlXLzG</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Gbetema MCHP (Fiama)</v>
+        <v>Masamboi MCHP</v>
       </c>
       <c r="B348" t="str">
-        <v>as1dnmlXLzG</v>
+        <v>Hu31NCRjZlj</v>
       </c>
     </row>
     <row r="349">
@@ -4521,18 +4521,18 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Kpetema MCHP</v>
+        <v>Ngueh MCHP</v>
       </c>
       <c r="B452" t="str">
-        <v>kDxbU1uSBFh</v>
+        <v>Vw4Uv6UPIPC</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Ngueh MCHP</v>
+        <v>Kpetema MCHP</v>
       </c>
       <c r="B453" t="str">
-        <v>Vw4Uv6UPIPC</v>
+        <v>kDxbU1uSBFh</v>
       </c>
     </row>
     <row r="454">
@@ -4681,18 +4681,18 @@
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Praise Foundation CHC</v>
+        <v>Mayassoh MCHP</v>
       </c>
       <c r="B472" t="str">
-        <v>wtdBuXDwZYQ</v>
+        <v>Z8Cm76B2726</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Mayassoh MCHP</v>
+        <v>Praise Foundation CHC</v>
       </c>
       <c r="B473" t="str">
-        <v>Z8Cm76B2726</v>
+        <v>wtdBuXDwZYQ</v>
       </c>
     </row>
     <row r="474">
@@ -4969,18 +4969,18 @@
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Rosint Buya MCHP</v>
+        <v>Sahn Bumpe MCHP</v>
       </c>
       <c r="B508" t="str">
-        <v>el8sgzyHuEe</v>
+        <v>NDqR2cWlVy3</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Sahn Bumpe MCHP</v>
+        <v>Rosint Buya MCHP</v>
       </c>
       <c r="B509" t="str">
-        <v>NDqR2cWlVy3</v>
+        <v>el8sgzyHuEe</v>
       </c>
     </row>
     <row r="510">
@@ -5169,18 +5169,18 @@
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Gbangba MCHP</v>
+        <v>Wai MCHP</v>
       </c>
       <c r="B533" t="str">
-        <v>r93q83kZoR9</v>
+        <v>zCSWBz2pyMd</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Wai MCHP</v>
+        <v>Gbangba MCHP</v>
       </c>
       <c r="B534" t="str">
-        <v>zCSWBz2pyMd</v>
+        <v>r93q83kZoR9</v>
       </c>
     </row>
     <row r="535">
@@ -5569,18 +5569,18 @@
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>kamba mamudia</v>
+        <v>Madina (BUM) CHC</v>
       </c>
       <c r="B583" t="str">
-        <v>zO5hgxxfU4T</v>
+        <v>gE3gEGZbQMi</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Madina (BUM) CHC</v>
+        <v>kamba mamudia</v>
       </c>
       <c r="B584" t="str">
-        <v>gE3gEGZbQMi</v>
+        <v>zO5hgxxfU4T</v>
       </c>
     </row>
     <row r="585">
@@ -5729,18 +5729,18 @@
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Gbendembu Wesleyan CHC</v>
+        <v>Bandasuma Fiama MCHP</v>
       </c>
       <c r="B603" t="str">
-        <v>YAuJ3fyoEuI</v>
+        <v>aF6iPGbrcRk</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Bandasuma Fiama MCHP</v>
+        <v>Gbendembu Wesleyan CHC</v>
       </c>
       <c r="B604" t="str">
-        <v>aF6iPGbrcRk</v>
+        <v>YAuJ3fyoEuI</v>
       </c>
     </row>
     <row r="605">
@@ -5929,18 +5929,18 @@
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Wordu CHP</v>
+        <v>Robat MCHP</v>
       </c>
       <c r="B628" t="str">
-        <v>bW5BaqrBM4K</v>
+        <v>gP6hn503KUX</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Robat MCHP</v>
+        <v>Wordu CHP</v>
       </c>
       <c r="B629" t="str">
-        <v>gP6hn503KUX</v>
+        <v>bW5BaqrBM4K</v>
       </c>
     </row>
     <row r="630">
@@ -5961,18 +5961,18 @@
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>SLRCS (Nongowa) clinic</v>
+        <v>Wellbody MCHP</v>
       </c>
       <c r="B632" t="str">
-        <v>Vnc2qIRLbyw</v>
+        <v>XuGfiry96Bg</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Wellbody MCHP</v>
+        <v>SLRCS (Nongowa) clinic</v>
       </c>
       <c r="B633" t="str">
-        <v>XuGfiry96Bg</v>
+        <v>Vnc2qIRLbyw</v>
       </c>
     </row>
     <row r="634">
@@ -6025,18 +6025,18 @@
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Bendu Mameima CHC</v>
+        <v>Kamba MCHP</v>
       </c>
       <c r="B640" t="str">
-        <v>amgb83zVxp5</v>
+        <v>cJ7omISg7gG</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Kamba MCHP</v>
+        <v>Bendu Mameima CHC</v>
       </c>
       <c r="B641" t="str">
-        <v>cJ7omISg7gG</v>
+        <v>amgb83zVxp5</v>
       </c>
     </row>
     <row r="642">
@@ -6737,18 +6737,18 @@
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>Kania (Masungbala) MCHP</v>
+        <v>Musaia CHP</v>
       </c>
       <c r="B729" t="str">
-        <v>RNGpZqutw3Y</v>
+        <v>sTOXJA2KcY2</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>Musaia CHP</v>
+        <v>Kania (Masungbala) MCHP</v>
       </c>
       <c r="B730" t="str">
-        <v>sTOXJA2KcY2</v>
+        <v>RNGpZqutw3Y</v>
       </c>
     </row>
     <row r="731">
@@ -6849,18 +6849,18 @@
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>Koakor MCHP</v>
+        <v>Sumbuya CHC</v>
       </c>
       <c r="B743" t="str">
-        <v>EQc3n1juPFn</v>
+        <v>W2KnxOMvmgE</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>Sumbuya CHC</v>
+        <v>Koakor MCHP</v>
       </c>
       <c r="B744" t="str">
-        <v>W2KnxOMvmgE</v>
+        <v>EQc3n1juPFn</v>
       </c>
     </row>
     <row r="745">
@@ -7081,18 +7081,18 @@
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>Gissiwolo MCHP</v>
+        <v>Rothatha MCHP</v>
       </c>
       <c r="B772" t="str">
-        <v>AekX8HBymng</v>
+        <v>KaevAHPgkA8</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>Rothatha MCHP</v>
+        <v>Gissiwolo MCHP</v>
       </c>
       <c r="B773" t="str">
-        <v>KaevAHPgkA8</v>
+        <v>AekX8HBymng</v>
       </c>
     </row>
     <row r="774">
@@ -7105,50 +7105,50 @@
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>Sebengu MCHP</v>
+        <v>Sengama MCHP</v>
       </c>
       <c r="B775" t="str">
-        <v>Jd7G0NYBTx1</v>
+        <v>MBtmOhLs7y1</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>Sengama MCHP</v>
+        <v>Sebengu MCHP</v>
       </c>
       <c r="B776" t="str">
-        <v>MBtmOhLs7y1</v>
+        <v>Jd7G0NYBTx1</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>Kpayama 1 MCHP</v>
+        <v>Ngiehun (Lower Bambara) MCHP</v>
       </c>
       <c r="B777" t="str">
-        <v>So2b8zJfcMa</v>
+        <v>m21WB5iqHAb</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>Ngiehun (Lower Bambara) MCHP</v>
+        <v>Kpayama 1 MCHP</v>
       </c>
       <c r="B778" t="str">
-        <v>m21WB5iqHAb</v>
+        <v>So2b8zJfcMa</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>Gbandiwulo CHP</v>
+        <v>Manewa MCHP</v>
       </c>
       <c r="B779" t="str">
-        <v>Vw6CNyFUeh9</v>
+        <v>CTnuuI55SOj</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>Manewa MCHP</v>
+        <v>Gbandiwulo CHP</v>
       </c>
       <c r="B780" t="str">
-        <v>CTnuuI55SOj</v>
+        <v>Vw6CNyFUeh9</v>
       </c>
     </row>
     <row r="781">
@@ -7161,18 +7161,18 @@
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>Gbindi CHP</v>
+        <v>Sandaru (Gaura) MCHP</v>
       </c>
       <c r="B782" t="str">
-        <v>LFpl1falVZi</v>
+        <v>hTGeTrwzrPi</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>Sandaru (Gaura) MCHP</v>
+        <v>Gbindi CHP</v>
       </c>
       <c r="B783" t="str">
-        <v>hTGeTrwzrPi</v>
+        <v>LFpl1falVZi</v>
       </c>
     </row>
     <row r="784">
@@ -7209,18 +7209,18 @@
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>Mandema CHP</v>
+        <v>Torkpumbu MCHP</v>
       </c>
       <c r="B788" t="str">
-        <v>WerHl8SDtRU</v>
+        <v>RJpiHpefEUw</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>Torkpumbu MCHP</v>
+        <v>Mandema CHP</v>
       </c>
       <c r="B789" t="str">
-        <v>RJpiHpefEUw</v>
+        <v>WerHl8SDtRU</v>
       </c>
     </row>
     <row r="790">
@@ -7681,26 +7681,26 @@
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>Needy CHC</v>
+        <v>Sienga CHP</v>
       </c>
       <c r="B847" t="str">
-        <v>UOJlcpPnBat</v>
+        <v>a1E6QWBTEwX</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>Sienga CHP</v>
+        <v>Needy CHC</v>
       </c>
       <c r="B848" t="str">
-        <v>a1E6QWBTEwX</v>
+        <v>UOJlcpPnBat</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>Mayakie MCHP</v>
+        <v>New Maforkie CHP</v>
       </c>
       <c r="B849" t="str">
-        <v>R0CmUlFULXg</v>
+        <v>lzz1UhTzO4E</v>
       </c>
     </row>
     <row r="850">
@@ -7713,10 +7713,10 @@
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>New Maforkie CHP</v>
+        <v>Mayakie MCHP</v>
       </c>
       <c r="B851" t="str">
-        <v>lzz1UhTzO4E</v>
+        <v>R0CmUlFULXg</v>
       </c>
     </row>
     <row r="852">
@@ -7849,18 +7849,18 @@
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>Njama MCHP</v>
+        <v>Bongor MCHP</v>
       </c>
       <c r="B868" t="str">
-        <v>WMj6mBDw76A</v>
+        <v>zAyK28LLaez</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>Bongor MCHP</v>
+        <v>Njama MCHP</v>
       </c>
       <c r="B869" t="str">
-        <v>zAyK28LLaez</v>
+        <v>WMj6mBDw76A</v>
       </c>
     </row>
     <row r="870">
@@ -7873,18 +7873,18 @@
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>Konjo MCHP</v>
+        <v>SLRCS (Freetown) Clinic</v>
       </c>
       <c r="B871" t="str">
-        <v>d7hw1ababST</v>
+        <v>EmTN0L4EAVi</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>SLRCS (Freetown) Clinic</v>
+        <v>Konjo MCHP</v>
       </c>
       <c r="B872" t="str">
-        <v>EmTN0L4EAVi</v>
+        <v>d7hw1ababST</v>
       </c>
     </row>
     <row r="873">
@@ -7969,18 +7969,18 @@
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>Kambama CHP</v>
+        <v>Sandayeima MCHP</v>
       </c>
       <c r="B883" t="str">
-        <v>mYMJHVqdBKt</v>
+        <v>oUR5HPmim7E</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>Sandayeima MCHP</v>
+        <v>Kambama CHP</v>
       </c>
       <c r="B884" t="str">
-        <v>oUR5HPmim7E</v>
+        <v>mYMJHVqdBKt</v>
       </c>
     </row>
     <row r="885">
@@ -8369,18 +8369,18 @@
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>Mende Buima MCHP</v>
+        <v>Tissana MCHP</v>
       </c>
       <c r="B933" t="str">
-        <v>NnGUNkc5Zq8</v>
+        <v>SptGAcmbgPz</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>Tissana MCHP</v>
+        <v>Mende Buima MCHP</v>
       </c>
       <c r="B934" t="str">
-        <v>SptGAcmbgPz</v>
+        <v>NnGUNkc5Zq8</v>
       </c>
     </row>
     <row r="935">
@@ -8673,18 +8673,18 @@
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>Kondeya (Sandor) MCHP</v>
+        <v>Mokorbu MCHP</v>
       </c>
       <c r="B971" t="str">
-        <v>e5sGsWLEn3k</v>
+        <v>cHqboEGRUiY</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>Mokorbu MCHP</v>
+        <v>Kondeya (Sandor) MCHP</v>
       </c>
       <c r="B972" t="str">
-        <v>cHqboEGRUiY</v>
+        <v>e5sGsWLEn3k</v>
       </c>
     </row>
     <row r="973">
@@ -8761,26 +8761,26 @@
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>Mabang MCHP</v>
+        <v>Mano Yorgbo MCHP</v>
       </c>
       <c r="B982" t="str">
-        <v>fCFdj2T0Bq1</v>
+        <v>KvE0PYQzXMM</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>Mano Yorgbo MCHP</v>
+        <v>Gloucester CHP</v>
       </c>
       <c r="B983" t="str">
-        <v>KvE0PYQzXMM</v>
+        <v>HTDuY3uxj6u</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>Gloucester CHP</v>
+        <v>Mabang MCHP</v>
       </c>
       <c r="B984" t="str">
-        <v>HTDuY3uxj6u</v>
+        <v>fCFdj2T0Bq1</v>
       </c>
     </row>
     <row r="985">
@@ -9073,18 +9073,18 @@
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>Laleihun Kovoma CHC</v>
+        <v>Sumbaria MCHP</v>
       </c>
       <c r="B1021" t="str">
-        <v>N3tpEjZcPm9</v>
+        <v>GvstqlRRnpV</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>Sumbaria MCHP</v>
+        <v>Laleihun Kovoma CHC</v>
       </c>
       <c r="B1022" t="str">
-        <v>GvstqlRRnpV</v>
+        <v>N3tpEjZcPm9</v>
       </c>
     </row>
     <row r="1023">
@@ -9209,10 +9209,10 @@
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>Mosanda CHP</v>
+        <v>Pewama CHP</v>
       </c>
       <c r="B1038" t="str">
-        <v>cDRQOxX1wHO</v>
+        <v>nbMpoRiVRWd</v>
       </c>
     </row>
     <row r="1039">
@@ -9225,10 +9225,10 @@
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v>Pewama CHP</v>
+        <v>Mosanda CHP</v>
       </c>
       <c r="B1040" t="str">
-        <v>nbMpoRiVRWd</v>
+        <v>cDRQOxX1wHO</v>
       </c>
     </row>
     <row r="1041">
@@ -9289,18 +9289,18 @@
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>Komendeh (Nongowa) MCHP</v>
+        <v>Rolembray MCHP</v>
       </c>
       <c r="B1048" t="str">
-        <v>NqwvaQC1ni4</v>
+        <v>nZblzPvJ5UW</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>Rolembray MCHP</v>
+        <v>Komendeh (Nongowa) MCHP</v>
       </c>
       <c r="B1049" t="str">
-        <v>nZblzPvJ5UW</v>
+        <v>NqwvaQC1ni4</v>
       </c>
     </row>
     <row r="1050">
@@ -9377,18 +9377,18 @@
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>Yele CHC</v>
+        <v>Mabolleh MCHP</v>
       </c>
       <c r="B1059" t="str">
-        <v>sesv0eXljBq</v>
+        <v>PybxeRWVSrI</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>Mabolleh MCHP</v>
+        <v>Yele CHC</v>
       </c>
       <c r="B1060" t="str">
-        <v>PybxeRWVSrI</v>
+        <v>sesv0eXljBq</v>
       </c>
     </row>
     <row r="1061">
@@ -9665,18 +9665,18 @@
     </row>
     <row r="1095">
       <c r="A1095" t="str">
-        <v>Gbalan Thallan MCHP</v>
+        <v>Tonko Maternity Clinic</v>
       </c>
       <c r="B1095" t="str">
-        <v>FsunWIQLXoF</v>
+        <v>uNEhNuBUr0i</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="str">
-        <v>Tonko Maternity Clinic</v>
+        <v>Gbalan Thallan MCHP</v>
       </c>
       <c r="B1096" t="str">
-        <v>uNEhNuBUr0i</v>
+        <v>FsunWIQLXoF</v>
       </c>
     </row>
     <row r="1097">
@@ -9793,18 +9793,18 @@
     </row>
     <row r="1111">
       <c r="A1111" t="str">
-        <v>Bumban MCHP</v>
+        <v>Tagrin CHC</v>
       </c>
       <c r="B1111" t="str">
-        <v>OI0BQUurVFS</v>
+        <v>O63vIA5MVn6</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="str">
-        <v>Tagrin CHC</v>
+        <v>Bumban MCHP</v>
       </c>
       <c r="B1112" t="str">
-        <v>O63vIA5MVn6</v>
+        <v>OI0BQUurVFS</v>
       </c>
     </row>
     <row r="1113">
@@ -9953,18 +9953,18 @@
     </row>
     <row r="1131">
       <c r="A1131" t="str">
-        <v>Gbongeima MCHP</v>
+        <v>Lion for Lion Clinic</v>
       </c>
       <c r="B1131" t="str">
-        <v>rebbn0ooFSO</v>
+        <v>cZxP4NE5O9z</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="str">
-        <v>Lion for Lion Clinic</v>
+        <v>Gbongeima MCHP</v>
       </c>
       <c r="B1132" t="str">
-        <v>cZxP4NE5O9z</v>
+        <v>rebbn0ooFSO</v>
       </c>
     </row>
     <row r="1133">
@@ -10201,18 +10201,18 @@
     </row>
     <row r="1162">
       <c r="A1162" t="str">
-        <v>Mabang CHC</v>
+        <v>Gbonkobana CHP</v>
       </c>
       <c r="B1162" t="str">
-        <v>Ahh47q8AkId</v>
+        <v>BXJnMD2eJAx</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="str">
-        <v>Gbonkobana CHP</v>
+        <v>Mabang CHC</v>
       </c>
       <c r="B1163" t="str">
-        <v>BXJnMD2eJAx</v>
+        <v>Ahh47q8AkId</v>
       </c>
     </row>
     <row r="1164">
